--- a/tools/excel/canada/pipeda.xlsx
+++ b/tools/excel/canada/pipeda.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Government of Canada</t>
+          <t>Government of Canada. Reproduced under the Reproduction of Federal Law Order (SI/97-5); this is not an official version.</t>
         </is>
       </c>
     </row>
@@ -582,6 +582,18 @@
           <t>Loi fédérale canadienne sur la protection des renseignements personnels dans le secteur privé, régissant la collecte, l'utilisation et la communication de renseignements personnels dans le cadre d'activités commerciales.
 L.C. 2000, ch. 5. L'annexe 1 énonce les 10 principes énoncés dans le Code type sur la protection des renseignements personnels.
 https://laws-lois.justice.gc.ca/fra/lois/P-8.6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>publication_date</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
         </is>
       </c>
     </row>
@@ -710,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -765,7 +777,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Schedule 1</t>
+          <t>Schedule-1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -825,13 +837,11 @@
           <t>4.1.1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Accountability for the organization's compliance with the principles rests with the designated individual(s), even though other individuals within the organization may be responsible for the day-to-day collection and processing of personal information. In addition, other individuals within the organization may be delegated to act on behalf of the designated individual(s).</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Il incombe à la ou aux personnes désignées de s'assurer que l'organisation respecte les principes même si d'autres membres de l'organisation peuvent être chargés de la collecte et du traitement quotidiens des renseignements personnels. D'autres membres de l'organisation peuvent aussi être délégués pour agir au nom de la ou des personnes désignées.</t>
@@ -852,13 +862,11 @@
           <t>4.1.2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>The identity of the individual(s) designated by the organization to oversee the organization's compliance with the principles shall be made known upon request.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Il doit être possible de connaître sur demande l'identité des personnes que l'organisation a désignées pour s'assurer que les principes sont respectés.</t>
@@ -879,13 +887,11 @@
           <t>4.1.3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>An organization is responsible for personal information in its possession or custody, including information that has been transferred to a third party for processing. The organization shall use contractual or other means to provide a comparable level of protection while the information is being processed by a third party.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Une organisation est responsable des renseignements personnels qu'elle a en sa possession ou sous sa garde, y compris les renseignements confiés à une tierce partie aux fins de traitement. L'organisation doit, par voie contractuelle ou autre, fournir un degré comparable de protection aux renseignements qui sont en cours de traitement par une tierce partie.</t>
@@ -906,13 +912,11 @@
           <t>4.1.4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Organizations shall implement policies and practices to give effect to the principles, including (a) implementing procedures to protect personal information; (b) establishing procedures to receive and respond to complaints and inquiries; (c) training staff and communicating to staff information about the organization's policies and practices; and (d) developing information to explain the organization's policies and procedures.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Les organisations doivent assurer la mise en oeuvre des politiques et des pratiques destinées à donner suite aux principes, y compris : a) la mise en oeuvre des procédures pour protéger les renseignements personnels; b) la mise en place des procédures pour recevoir les plaintes et les demandes de renseignements et y donner suite; c) la formation du personnel et la transmission au personnel de l'information relative aux politiques et pratiques de l'organisation; et d) la rédaction des documents explicatifs concernant leurs politiques et procédures.</t>
@@ -963,13 +967,11 @@
           <t>4.2.1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>The organization shall document the purposes for which personal information is collected in order to comply with the Openness principle (Clause 4.8) and the Individual Access principle (Clause 4.9).</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>L'organisation doit documenter les fins auxquelles les renseignements personnels sont recueillis afin de se conformer au principe de la transparence (article 4.8) et au principe de l'accès aux renseignements personnels (article 4.9).</t>
@@ -977,11 +979,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
@@ -990,13 +987,11 @@
           <t>4.2.2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Identifying the purposes for which personal information is collected at or before the time of collection allows organizations to determine the information they need to collect to fulfil these purposes. The Limiting Collection principle (Clause 4.4) requires an organization to collect only that information necessary for the purposes that have been identified.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Le fait de préciser les fins de la collecte de renseignements personnels avant celle-ci ou au moment de celle-ci permet à l'organisation de déterminer les renseignements dont elle a besoin pour réaliser les fins mentionnées. Suivant le principe de la limitation en matière de collecte (article 4.4), l'organisation ne doit recueillir que les renseignements nécessaires aux fins mentionnées.</t>
@@ -1017,13 +1012,11 @@
           <t>4.2.3</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>The identified purposes should be specified at or before the time of collection to the individual from whom the personal information is collected. Depending upon the way in which the information is collected, this can be done orally or in writing. An application form, for example, may give notice of the purposes.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Il faudrait préciser à la personne auprès de laquelle on recueille des renseignements, avant la collecte ou au moment de celle-ci, les fins auxquelles ils sont destinés. Selon la façon dont se fait la collecte, cette précision peut être communiquée de vive voix ou par écrit. Par exemple, on peut indiquer ces fins sur un formulaire de demande de renseignements.</t>
@@ -1044,13 +1037,11 @@
           <t>4.2.4</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>When personal information that has been collected is to be used for a purpose not previously identified, the new purpose shall be identified prior to use. Unless the new purpose is required by law, the consent of the individual is required before information can be used for that purpose. For an elaboration on consent, please refer to the Consent principle (Clause 4.3).</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Avant de se servir de renseignements personnels à des fins non précisées antérieurement, les nouvelles fins doivent être précisées avant l'utilisation. À moins que les nouvelles fins auxquelles les renseignements sont destinés ne soient prévues par une loi, il faut obtenir le consentement de la personne concernée avant d'utiliser les renseignements à cette nouvelle fin. Pour obtenir plus de précisions sur le consentement, se reporter au principe du consentement (article 4.3).</t>
@@ -1071,13 +1062,11 @@
           <t>4.2.5</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Persons collecting personal information should be able to explain to individuals the purposes for which the information is being collected.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Les personnes qui recueillent des renseignements personnels devraient être en mesure d'expliquer à la personne concernée à quelles fins sont destinés ces renseignements.</t>
@@ -1085,11 +1074,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
@@ -1098,13 +1082,11 @@
           <t>4.2.6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>This principle is linked closely to the Limiting Collection principle (Clause 4.4) and the Limiting Use, Disclosure, and Retention principle (Clause 4.5).</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Ce principe est étroitement lié au principe de la limitation de la collecte (article 4.4) et à celui de la limitation de l'utilisation, de la communication et de la conservation (article 4.5).</t>
@@ -1155,13 +1137,11 @@
           <t>4.3.1</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Consent is required for the collection of personal information and the subsequent use or disclosure of this information. Typically, an organization will seek consent for the use or disclosure of the information at the time of collection. In certain circumstances, consent with respect to use or disclosure may be sought after the information has been collected but before use (for example, when an organization wants to use information for a purpose not previously identified).</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Il faut obtenir le consentement de la personne concernée avant de recueillir des renseignements personnels à son sujet et d'utiliser ou de communiquer les renseignements recueillis. Généralement, une organisation obtient le consentement des personnes concernées relativement à l'utilisation et à la communication des renseignements personnels au moment de la collecte. Dans certains cas, une organisation peut obtenir le consentement concernant l'utilisation ou la communication des renseignements après avoir recueilli ces renseignements, mais avant de s'en servir, par exemple, quand elle veut les utiliser à des fins non précisées antérieurement.</t>
@@ -1182,13 +1162,11 @@
           <t>4.3.2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>The principle requires “knowledge and consent”. Organizations shall make a reasonable effort to ensure that the individual is advised of the purposes for which the information will be used. To make the consent meaningful, the purposes must be stated in such a manner that the individual can reasonably understand how the information will be used or disclosed.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Suivant ce principe, il faut informer la personne au sujet de laquelle on recueille des renseignements et obtenir son consentement. Les organisations doivent faire un effort raisonnable pour s'assurer que la personne est informée des fins auxquelles les renseignements seront utilisés. Pour que le consentement soit valable, les fins doivent être énoncées de façon que la personne puisse raisonnablement comprendre de quelle manière les renseignements seront utilisés ou communiqués.</t>
@@ -1209,13 +1187,11 @@
           <t>4.3.3</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>An organization shall not, as a condition of the supply of a product or service, require an individual to consent to the collection, use, or disclosure of information beyond that required to fulfil the explicitly specified, and legitimate purposes.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Une organisation ne peut pas, pour le motif qu'elle fournit un bien ou un service, exiger d'une personne qu'elle consente à la collecte, à l'utilisation ou à la communication de renseignements autres que ceux qui sont nécessaires pour réaliser les fins légitimes et explicitement indiquées.</t>
@@ -1236,13 +1212,11 @@
           <t>4.3.4</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The form of the consent sought by the organization may vary, depending upon the circumstances and the type of information. In determining the form of consent to use, organizations shall take into account the sensitivity of the information. Although some information (for example, medical records and income records) is almost always considered to be sensitive, any information can be sensitive, depending on the context. For example, the names and addresses of subscribers to a newsmagazine would generally not be considered sensitive information. However, the names and addresses of subscribers to some special-interest magazines might be considered sensitive.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>La forme du consentement que l'organisation cherche à obtenir peut varier selon les circonstances et la nature des renseignements. Pour déterminer la forme que prendra le consentement, les organisations doivent tenir compte de la sensibilité des renseignements. Si certains renseignements sont presque toujours considérés comme sensibles, par exemple les dossiers médicaux et le revenu, tous les renseignements peuvent devenir sensibles suivant le contexte. Par exemple, les nom et adresse des abonnés d'une revue d'information ne seront généralement pas considérés comme des renseignements sensibles. Toutefois, les nom et adresse des abonnés de certains périodiques spécialisés pourront l'être.</t>
@@ -1263,16 +1237,14 @@
           <t>4.3.5</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>In obtaining consent, the reasonable expectations of the individual are also relevant. For example, an individual buying a subscription to a magazine should reasonably expect that the organization, in addition to using the individual's name and address for mailing and billing purposes, would also contact the person to solicit the renewal of the subscription. In this case, the organization can assume that the individual's request constitutes consent for specific purposes. On the other hand, an individual would not reasonably expect that personal information given to a health-care professional would be given to a company selling health-care products, unless consent were obtained. Consent shall not be obtained through deception.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Dans l'obtention du consentement, les attentes raisonnables de la personne sont aussi pertinentes. Par exemple, une personne qui s'abonne à un périodique devrait raisonnablement s'attendre à ce que l'entreprise, en plus de se servir de son nom et de son adresse à des fins de postage et de facturation, communique avec elle pour lui demander si elle désire que son abonnement soit renouvelé. Dans ce cas, l'organisation peut présumer que la demande de la personne constitue un consentement à ces fins précises. D'un autre côté, il n'est pas raisonnable qu'une personne s'attende à ce que les renseignements personnels qu'elle fournit à un professionnel de la santé soient donnés sans son consentement à une entreprise qui vend des produits de soins de santé. Le consentement ne doit pas être obtenu par un subterfüge.</t>
+          <t>Dans l'obtention du consentement, les attentes raisonnables de la personne sont aussi pertinentes. Par exemple, une personne qui s'abonne à un périodique devrait raisonnablement s'attendre à ce que l'entreprise, en plus de se servir de son nom et de son adresse à des fins de postage et de facturation, communique avec elle pour lui demander si elle désire que son abonnement soit renouvelé. Dans ce cas, l'organisation peut présumer que la demande de la personne constitue un consentement à ces fins précises. D'un autre côté, il n'est pas raisonnable qu'une personne s'attende à ce que les renseignements personnels qu'elle fournit à un professionnel de la santé soient donnés sans son consentement à une entreprise qui vend des produits de soins de santé. Le consentement ne doit pas être obtenu par un subterfuge.</t>
         </is>
       </c>
     </row>
@@ -1290,13 +1262,11 @@
           <t>4.3.6</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>The way in which an organization seeks consent may vary, depending on the circumstances and the type of information collected. An organization should generally seek express consent when the information is likely to be considered sensitive. Implied consent would generally be appropriate when the information is less sensitive. Consent can also be given by an authorized representative (such as a legal guardian or a person having power of attorney).</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>La façon dont une organisation obtient le consentement peut varier selon les circonstances et la nature des renseignements recueillis. En général, l'organisation devrait chercher à obtenir un consentement explicite si les renseignements sont susceptibles d'être considérés comme sensibles. Lorsque les renseignements sont moins sensibles, un consentement implicite serait normalement jugé suffisant. Le consentement peut également être donné par un représentant autorisé (détenteur d'une procuration, tuteur).</t>
@@ -1304,11 +1274,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
@@ -1317,13 +1282,11 @@
           <t>4.3.7</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Individuals can give consent in many ways. For example: (a) an application form may be used to seek consent, collect information, and inform the individual of the use that will be made of the information. By completing and signing the form, the individual is giving consent to the collection and the specified uses; (b) a checkoff box may be used to allow individuals to request that their names and addresses not be given to other organizations. Individuals who do not check the box are assumed to consent to the transfer of this information to third parties; (c) consent may be given orally when information is collected over the telephone; or (d) consent may be given at the time that individuals use a product or service.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Le consentement peut revêtir différentes formes, par exemple : a) on peut se servir d'un formulaire de demande de renseignements pour obtenir le consentement, recueillir des renseignements et informer la personne de l'utilisation qui sera faite des renseignements. En remplissant le formulaire et en le signant, la personne donne son consentement à la collecte de renseignements et aux usages précisés; b) on peut prévoir une case où la personne pourra indiquer en cochant qu'elle refuse que ses nom et adresse soient communiqués à d'autres organisations. Si la personne ne coche pas la case, il sera présumé qu'elle consent à ce que les renseignements soient communiqués à des tiers; c) le consentement peut être donné de vive voix lorsque les renseignements sont recueillis par téléphone; ou d) le consentement peut être donné au moment où le produit ou le service est utilisé.</t>
@@ -1344,13 +1307,11 @@
           <t>4.3.8</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>An individual may withdraw consent at any time, subject to legal or contractual restrictions and reasonable notice. The organization shall inform the individual of the implications of such withdrawal.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Une personne peut retirer son consentement en tout temps, sous réserve de restrictions prévues par une loi ou un contrat et d'un préavis raisonnable. L'organisation doit informer la personne des conséquences d'un tel retrait.</t>
@@ -1401,13 +1362,11 @@
           <t>4.4.1</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Organizations shall not collect personal information indiscriminately. Both the amount and the type of information collected shall be limited to that which is necessary to fulfil the purposes identified. Organizations shall specify the type of information collected as part of their information-handling policies and practices, in accordance with the Openness principle (Clause 4.8).</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Les organisations ne doivent pas recueillir des renseignements de façon arbitraire. On doit restreindre tant la quantité que la nature des renseignements recueillis à ce qui est nécessaire pour réaliser les fins déterminées. Conformément au principe de la transparence (article 4.8), les organisations doivent préciser la nature des renseignements recueillis comme partie intégrante de leurs politiques et pratiques concernant le traitement des renseignements.</t>
@@ -1428,25 +1387,18 @@
           <t>4.4.2</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>The requirement that personal information be collected by fair and lawful means is intended to prevent organizations from collecting information by misleading or deceiving individuals about the purpose for which information is being collected. This requirement implies that consent with respect to collection must not be obtained through deception.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>L'exigence selon laquelle les organisations sont tenues de recueillir des renseignements personnels de façon honnête et licite a pour objet de les empêcher de tromper les gens et de les induire en erreur quant aux fins auxquelles les renseignements sont recueillis. Cette obligation suppose que le consentement à la collecte de renseignements ne doit pas être obtenu par un subterfüge.</t>
+          <t>L'exigence selon laquelle les organisations sont tenues de recueillir des renseignements personnels de façon honnête et licite a pour objet de les empêcher de tromper les gens et de les induire en erreur quant aux fins auxquelles les renseignements sont recueillis. Cette obligation suppose que le consentement à la collecte de renseignements ne doit pas être obtenu par un subterfuge.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
@@ -1455,13 +1407,11 @@
           <t>4.4.3</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>This principle is linked closely to the Identifying Purposes principle (Clause 4.2) and the Consent principle (Clause 4.3).</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Ce principe est étroitement lié au principe de détermination des fins auxquelles la collecte est destinée (article 4.2) et à celui du consentement (article 4.3).</t>
@@ -1512,13 +1462,11 @@
           <t>4.5.1</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Organizations using personal information for a new purpose shall document this purpose (see Clause 4.2.1).</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Les organisations qui se servent de renseignements personnels à des fins nouvelles doivent documenter ces fins (voir article 4.2.1).</t>
@@ -1539,13 +1487,11 @@
           <t>4.5.2</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Organizations should develop guidelines and implement procedures with respect to the retention of personal information. These guidelines should include minimum and maximum retention periods. Personal information that has been used to make a decision about an individual shall be retained long enough to allow the individual access to the information after the decision has been made. An organization may be subject to legislative requirements with respect to retention periods.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Les organisations devraient élaborer des lignes directrices et appliquer des procédures pour la conservation des renseignements personnels. Ces lignes directrices devraient préciser les durées minimales et maximales de conservation. On doit conserver les renseignements personnels servant à prendre une décision au sujet d'une personne suffisamment longtemps pour permettre à la personne concernée d'exercer son droit d'accès à l'information après que la décision a été prise. Une organisation peut être assujettie à des exigences prévues par la loi en ce qui concerne les périodes de conservation.</t>
@@ -1566,13 +1512,11 @@
           <t>4.5.3</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Personal information that is no longer required to fulfil the identified purposes should be destroyed, erased, or made anonymous. Organizations shall develop guidelines and implement procedures to govern the destruction of personal information.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>On devrait détruire, effacer ou dépersonnaliser les renseignements personnels dont on n'a plus besoin aux fins précisées. Les organisations doivent élaborer des lignes directrices et appliquer des procédures régissant la destruction des renseignements personnels.</t>
@@ -1580,11 +1524,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
@@ -1593,13 +1532,11 @@
           <t>4.5.4</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>This principle is closely linked to the Consent principle (Clause 4.3), the Identifying Purposes principle (Clause 4.2), and the Individual Access principle (Clause 4.9).</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Ce principe est étroitement lié au principe du consentement (article 4.3), à celui de la détermination des fins auxquelles la collecte est destinée (article 4.2), ainsi qu'à celui de l'accès individuel (article 4.9).</t>
@@ -1650,13 +1587,11 @@
           <t>4.6.1</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>The extent to which personal information shall be accurate, complete, and up-to-date will depend upon the use of the information, taking into account the interests of the individual. Information shall be sufficiently accurate, complete, and up-to-date to minimize the possibility that inappropriate information may be used to make a decision about the individual.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Le degré d'exactitude et de mise à jour ainsi que le caractère complet des renseignements personnels dépendront de l'usage auquel ils sont destinés, compte tenu des intérêts de la personne. Les renseignements doivent être suffisamment exacts, complets et à jour pour réduire au minimum la possibilité que des renseignements inappropriés soient utilisés pour prendre une décision à son sujet.</t>
@@ -1677,13 +1612,11 @@
           <t>4.6.2</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>An organization shall not routinely update personal information, unless such a process is necessary to fulfil the purposes for which the information was collected.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Une organisation ne doit pas systématiquement mettre à jour les renseignements personnels à moins que cela ne soit nécessaire pour atteindre les fins auxquelles ils ont été recueillis.</t>
@@ -1704,13 +1637,11 @@
           <t>4.6.3</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Personal information that is used on an ongoing basis, including information that is disclosed to third parties, should generally be accurate and up-to-date, unless limits to the requirement for accuracy are clearly set out.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Les renseignements personnels qui servent en permanence, y compris les renseignements qui sont communiqués à des tiers, devraient normalement être exacts et à jour à moins que des limites se rapportant à l'exactitude de ces renseignements ne soient clairement établies.</t>
@@ -1761,13 +1692,11 @@
           <t>4.7.1</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>The security safeguards shall protect personal information against loss or theft, as well as unauthorized access, disclosure, copying, use, or modification. Organizations shall protect personal information regardless of the format in which it is held.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Les mesures de sécurité doivent protéger les renseignements personnels contre la perte ou le vol ainsi que contre la consultation, la communication, la copie, l'utilisation ou la modification non autorisées. Les organisations doivent protéger les renseignements personnels quelle que soit la forme sous laquelle ils sont conservés.</t>
@@ -1788,13 +1717,11 @@
           <t>4.7.2</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>The nature of the safeguards will vary depending on the sensitivity of the information that has been collected, the amount, distribution, and format of the information, and the method of storage. More sensitive information should be safeguarded by a higher level of protection. The concept of sensitivity is discussed in Clause 4.3.4.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>La nature des mesures de sécurité variera en fonction du degré de sensibilité des renseignements personnels recueillis, de la quantité, de la répartition et du format des renseignements personnels ainsi que des méthodes de conservation. Les renseignements plus sensibles devraient être mieux protégés. La notion de sensibilité est présentée à l'article 4.3.4.</t>
@@ -1815,13 +1742,11 @@
           <t>4.7.3</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>The methods of protection should include (a) physical measures, for example, locked filing cabinets and restricted access to offices; (b) organizational measures, for example, security clearances and limiting access on a “need-to-know” basis; and (c) technological measures, for example, the use of passwords and encryption.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Les méthodes de protection devraient comprendre : a) des moyens matériels, par exemple le verrouillage des classeurs et la restriction de l'accès aux bureaux; b) des mesures administratives, par exemple des autorisations sécuritaires et un accès sélectif; et c) des mesures techniques, par exemple l'usage de mots de passe et du chiffrement.</t>
@@ -1842,13 +1767,11 @@
           <t>4.7.4</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Organizations shall make their employees aware of the importance of maintaining the confidentiality of personal information.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Les organisations doivent sensibiliser leur personnel à l'importance de protéger le caractère confidentiel des renseignements personnels.</t>
@@ -1869,13 +1792,11 @@
           <t>4.7.5</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Care shall be used in the disposal or destruction of personal information, to prevent unauthorized parties from gaining access to the information (see Clause 4.5.3).</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Au moment du retrait ou de la destruction des renseignements personnels, on doit veiller à empêcher les personnes non autorisées d'y avoir accès (article 4.5.3).</t>
@@ -1926,13 +1847,11 @@
           <t>4.8.1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Organizations shall be open about their policies and practices with respect to the management of personal information. Individuals shall be able to acquire information about an organization's policies and practices without unreasonable effort. This information shall be made available in a form that is generally understandable.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Les organisations doivent faire preuve de transparence au sujet de leurs politiques et pratiques concernant la gestion des renseignements personnels. Une personne doit pouvoir obtenir sans efforts déraisonnables de l'information au sujet des politiques et des pratiques d'une organisation. Ces renseignements doivent être fournis sous une forme généralement compréhensible.</t>
@@ -1953,13 +1872,11 @@
           <t>4.8.2</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>The information made available shall include (a) the name or title, and the address, of the person who is accountable for the organization's policies and practices and to whom complaints or inquiries can be forwarded; (b) the means of gaining access to personal information held by the organization; (c) a description of the type of personal information held by the organization, including a general account of its use; (d) a copy of any brochures or other information that explain the organization's policies, standards, or codes; and (e) what personal information is made available to related organizations (e.g., subsidiaries).</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Les renseignements fournis doivent comprendre : a) le nom ou la fonction de même que l'adresse de la personne responsable de la politique et des pratiques de l'organisation et à qui il faut acheminer les plaintes et les demandes de renseignements; b) la description du moyen d'accès aux renseignements personnels que possède l'organisation; c) la description du genre de renseignements personnels que possède l'organisation, y compris une explication générale de l'usage auquel ils sont destinés; d) une copie de toute brochure ou autre document d'information expliquant la politique, les normes ou les codes de l'organisation; et e) la définition de la nature des renseignements personnels communiqués aux organisations connexes (par exemple, les filiales).</t>
@@ -1967,11 +1884,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="B46" t="n">
         <v>3</v>
       </c>
@@ -1980,16 +1892,14 @@
           <t>4.8.3</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>An organization may make information on its policies and practices available in a variety of ways. The method chosen depends on the nature of its business and other considerations. For example, an organization may choose to make brochures available in its place of business, mail information to its customers, provide online access, or establish a toll-free telephone number.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Une organisation peut rendre l'information concernant sa politique et ses pratiques accessible de diverses façons. La méthode choisie est fonction de la nature des activités de l'organisation et d'autres considérations. Par exemple, une organisation peut offrir des brochures à son établissement, poster des renseignements à ses clients, offrir un accès en ligne ou établir un numéro de téléphone sans frais.</t>
+          <t>Une organisation peut rendre l'information concernant sa politique et ses pratiques accessibles de diverses façons. La méthode choisie est fonction de la nature des activités de l'organisation et d'autres considérations. Par exemple, une organisation peut offrir des brochures à son établissement, poster des renseignements à ses clients, offrir un accès en ligne ou établir un numéro de téléphone sans frais.</t>
         </is>
       </c>
     </row>
@@ -2037,13 +1947,11 @@
           <t>4.9.1</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Upon request, an organization shall inform an individual whether or not the organization holds personal information about the individual. Organizations are encouraged to indicate the source of this information. The organization shall allow the individual access to this information. However, the organization may choose to make sensitive medical information available through a medical practitioner. In addition, the organization shall provide an account of the use that has been made or is being made of this information and an account of the third parties to which it has been disclosed.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Une organisation doit informer la personne qui en fait la demande du fait qu'elle possède des renseignements personnels à son sujet, le cas échéant. Les organisations sont invitées à indiquer la source des renseignements. L'organisation doit permettre à la personne concernée de consulter ces renseignements. Dans le cas de renseignements médicaux sensibles, l'organisation peut préférer que ces renseignements soient communiqués par un médecin. En outre, l'organisation doit informer la personne concernée de l'usage qu'elle fait ou a fait des renseignements et des tiers à qui ils ont été communiqués.</t>
@@ -2064,13 +1972,11 @@
           <t>4.9.2</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>An individual may be required to provide sufficient information to permit an organization to provide an account of the existence, use, and disclosure of personal information. The information provided shall only be used for this purpose.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Une organisation peut exiger que la personne concernée lui fournisse suffisamment de renseignements pour qu'il lui soit possible de la renseigner sur l'existence, l'utilisation et la communication de renseignements personnels. L'information ainsi fournie doit servir à cette seule fin.</t>
@@ -2091,13 +1997,11 @@
           <t>4.9.3</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>In providing an account of third parties to which it has disclosed personal information about an individual, an organization should attempt to be as specific as possible. When it is not possible to provide a list of the organizations to which it has actually disclosed information about an individual, the organization shall provide a list of organizations to which it may have disclosed information about the individual.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>L'organisation qui fournit le relevé des tiers à qui elle a communiqué des renseignements personnels au sujet d'une personne devrait être la plus précise possible. S'il lui est impossible de fournir une liste des organisations à qui elle a effectivement communiqué des renseignements au sujet d'une personne, l'organisation doit fournir une liste des organisations à qui elle pourrait avoir communiqué de tels renseignements.</t>
@@ -2118,13 +2022,11 @@
           <t>4.9.4</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>An organization shall respond to an individual's request within a reasonable time and at minimal or no cost to the individual. The requested information shall be provided or made available in a form that is generally understandable. For example, if the organization uses abbreviations or codes to record information, an explanation shall be provided.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Une organisation qui reçoit une demande de communication de renseignements doit répondre dans un délai raisonnable et ne peut exiger, pour ce faire, que des droits minimes. Les renseignements demandés doivent être fournis sous une forme généralement compréhensible. Par exemple, l'organisation qui se sert d'abréviations ou de codes pour l'enregistrement des renseignements doit fournir les explications nécessaires.</t>
@@ -2145,13 +2047,11 @@
           <t>4.9.5</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
           <t>When an individual successfully demonstrates the inaccuracy or incompleteness of personal information, the organization shall amend the information as required. Depending upon the nature of the information challenged, amendment involves the correction, deletion, or addition of information. Where appropriate, the amended information shall be transmitted to third parties having access to the information in question.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Lorsqu'une personne démontre que des renseignements personnels sont inexacts ou incomplets, l'organisation doit apporter les modifications nécessaires à ces renseignements. Selon la nature des renseignements qui font l'objet de la contestation, l'organisation doit corriger, supprimer ou ajouter des renseignements. S'il y a lieu, l'information modifiée doit être communiquée à des tiers ayant accès à l'information en question.</t>
@@ -2172,13 +2072,11 @@
           <t>4.9.6</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
           <t>When a challenge is not resolved to the satisfaction of the individual, the substance of the unresolved challenge shall be recorded by the organization. When appropriate, the existence of the unresolved challenge shall be transmitted to third parties having access to the information in question.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Lorsqu'une contestation n'est pas réglée à la satisfaction de la personne concernée, l'organisation prend note de l'objet de la contestation. S'il y a lieu, les tierces parties ayant accès à l'information en question doivent être informées du fait que la contestation n'a pas été réglée.</t>
@@ -2216,11 +2114,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="B55" t="n">
         <v>3</v>
       </c>
@@ -2229,13 +2122,11 @@
           <t>4.10.1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>The individual accountable for an organization's compliance is discussed in Clause 4.1.1.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>La question de la désignation de la personne responsable du respect des principes dans l'organisation fait l'objet de l'article 4.1.1.</t>
@@ -2256,13 +2147,11 @@
           <t>4.10.2</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Organizations shall put procedures in place to receive and respond to complaints or inquiries about their policies and practices relating to the handling of personal information. The complaint procedures should be easily accessible and simple to use.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Les organisations doivent établir des procédures pour recevoir les plaintes et les demandes de renseignements concernant leurs politiques et pratiques de gestion des renseignements personnels et y donner suite. Les procédures relatives aux plaintes devraient être facilement accessibles et simples à utiliser.</t>
@@ -2283,13 +2172,11 @@
           <t>4.10.3</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Organizations shall inform individuals who make inquiries or lodge complaints of the existence of relevant complaint procedures. A range of these procedures may exist. For example, some regulatory bodies accept complaints about the personal-information handling practices of the companies they regulate.</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Les organisations doivent informer les personnes qui présentent une demande de renseignements ou déposent une plainte de l'existence des procédures pertinentes. Il peut exister un éventail de ces procédures. Par exemple, certaines autorités réglementaires acceptent les plaintes concernant les pratiques de gestion des renseignements personnels des entreprises relevant de leur compétence.</t>
@@ -2310,13 +2197,11 @@
           <t>4.10.4</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>An organization shall investigate all complaints. If a complaint is found to be justified, the organization shall take appropriate measures, including, if necessary, amending its policies and practices.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Une organisation doit faire enquête sur toutes les plaintes. Si une plainte est jugée fondée, l'organisation doit prendre les mesures appropriées, y compris la modification de ses politiques et de ses pratiques au besoin.</t>
@@ -2324,12 +2209,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="n">
-        <v>1</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Part 1</t>
+          <t>Part-1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2337,47 +2224,48 @@
           <t>Protection of Personal Information in the Private Sector</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Statutory provisions of PIPEDA governing private sector obligations, including breach reporting requirements.</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Partie 1 — Protection des renseignements personnels dans le secteur privé</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Dispositions législatives de la LPRPDE régissant les obligations du secteur privé, notamment les exigences de signalement des atteintes.</t>
+          <t>Protection des renseignements personnels dans le secteur privé</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="n">
-        <v>2</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>s. 10.1</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Breach of Security Safeguards</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory breach notification requirements for organizations subject to PIPEDA.</t>
+          <t>Appropriate purposes</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>An organization may collect, use or disclose personal information only for purposes that a reasonable person would consider are appropriate in the circumstances.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atteinte aux mesures de sécurité</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
+          <t>Fins acceptables</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>L’organisation ne peut recueillir, utiliser ou communiquer des renseignements personnels qu’à des fins qu’une personne raisonnable estimerait acceptables dans les circonstances.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2385,51 +2273,116 @@
           <t>x</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>3</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10.1.a</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>An organization that has reasonable grounds to believe that a breach of security safeguards has occurred shall report the breach to the Privacy Commissioner of Canada and notify any individual whose personal information is involved in the breach if it is reasonable in the circumstances to believe the breach creates a real risk of significant harm to the individual.</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Une organisation qui a des motifs raisonnables de croire qu'une atteinte aux mesures de sécurité s'est produite doit en aviser le Commissaire à la protection de la vie privée du Canada et notifier toute personne dont les renseignements personnels sont concernés, s'il y a lieu de croire que l'atteinte crée un risque réel de préjudice grave pour la personne.</t>
+          <t>7-3</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Disclosure without knowledge or consent</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>For the purpose of clause 4.3 of Schedule 1, and despite the note that accompanies that clause, an organization may disclose personal information without the knowledge or consent of the individual only if the disclosure is
+(a) made to, in the Province of Quebec, an advocate or notary or, in any other province, a barrister or solicitor who is representing the organization;
+(b) for the purpose of collecting a debt owed by the individual to the organization;
+(c) required to comply with a subpoena or warrant issued or an order made by a court, person or body with jurisdiction to compel the production of information, or to comply with rules of court relating to the production of records;
+(c.1) made to a government institution or part of a government institution that has made a request for the information, identified its lawful authority to obtain the information and indicated that
+(i) it suspects that the information relates to national security, the defence of Canada or the conduct of international affairs,
+(ii) the disclosure is requested for the purpose of enforcing any law of Canada, a province or a foreign jurisdiction, carrying out an investigation relating to the enforcement of any such law or gathering intelligence for the purpose of enforcing any such law,
+(iii) the disclosure is requested for the purpose of administering any law of Canada or a province, or
+(iv) the disclosure is requested for the purpose of communicating with the next of kin or authorized representative of an injured, ill or deceased individual;
+(c.2) made to the government institution mentioned in section 7 of the Proceeds of Crime (Money Laundering) and Terrorist Financing Act as required by that section;
+(d) made on the initiative of the organization to a government institution or a part of a government institution and the organization
+(i) has reasonable grounds to believe that the information relates to a contravention of the laws of Canada, a province or a foreign jurisdiction that has been, is being or is about to be committed, or
+(ii) suspects that the information relates to national security, the defence of Canada or the conduct of international affairs;
+(d.1) made to another organization and is reasonable for the purposes of investigating a breach of an agreement or a contravention of the laws of Canada or a province that has been, is being or is about to be committed and it is reasonable to expect that disclosure with the knowledge or consent of the individual would compromise the investigation;
+(d.2) made to another organization and is reasonable for the purposes of detecting or suppressing fraud or of preventing fraud that is likely to be committed and it is reasonable to expect that the disclosure with the knowledge or consent of the individual would compromise the ability to prevent, detect or suppress the fraud;
+(d.21) made to another organization under subsection 11.01(1) of the Proceeds of Crime (Money Laundering) and Terrorist Financing Act;
+(d.3) made on the initiative of the organization to a government institution, a part of a government institution or the individual’s next of kin or authorized representative and
+(i) the organization has reasonable grounds to believe that the individual has been, is or may be the victim of financial abuse,
+(ii) the disclosure is made solely for purposes related to preventing or investigating the abuse, and
+(iii) it is reasonable to expect that disclosure with the knowledge or consent of the individual would compromise the ability to prevent or investigate the abuse;
+(d.4) necessary to identify the individual who is injured, ill or deceased, made to a government institution, a part of a government institution or the individual’s next of kin or authorized representative and, if the individual is alive, the organization informs that individual in writing without delay of the disclosure;
+(e) made to a person who needs the information because of an emergency that threatens the life, health or security of an individual and, if the individual whom the information is about is alive, the organization informs that individual in writing without delay of the disclosure;
+(e.1) of information that is contained in a witness statement and the disclosure is necessary to assess, process or settle an insurance claim;
+(e.2) of information that was produced by the individual in the course of their employment, business or profession and the disclosure is consistent with the purposes for which the information was produced;
+(f) for statistical, or scholarly study or research, purposes that cannot be achieved without disclosing the information, it is impracticable to obtain consent and the organization informs the Commissioner of the disclosure before the information is disclosed;
+(g) made to an institution whose functions include the conservation of records of historic or archival importance, and the disclosure is made for the purpose of such conservation;
+(h) made after the earlier of
+(i) one hundred years after the record containing the information was created, and
+(ii) twenty years after the death of the individual whom the information is about;
+(h.1) of information that is publicly available and is specified by the regulations; or
+(h.2) [Repealed, 2015, c. 32, s. 6]
+(i) required by law.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Communication à l’insu de l’intéressé ou sans son consentement</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pour l’application de l’article 4.3 de l’annexe 1 et malgré la note afférente, l’organisation ne peut communiquer de renseignement personnel à l’insu de l’intéressé ou sans son consentement que dans les cas suivants :
+a) la communication est faite à un avocat — dans la province de Québec, à un avocat ou à un notaire — qui représente l’organisation;
+b) elle est faite en vue du recouvrement d’une créance que celle-ci a contre l’intéressé;
+c) elle est exigée par assignation, mandat ou ordonnance d’un tribunal, d’une personne ou d’un organisme ayant le pouvoir de contraindre à la production de renseignements ou exigée par des règles de procédure se rapportant à la production de documents;
+c.1) elle est faite à une institution gouvernementale — ou à une subdivision d’une telle institution — qui a demandé à obtenir le renseignement en mentionnant la source de l’autorité légitime étayant son droit de l’obtenir et le fait, selon le cas :
+(i) qu’elle soupçonne que le renseignement est afférent à la sécurité nationale, à la défense du Canada ou à la conduite des affaires internationales,
+(ii) que la communication est demandée aux fins du contrôle d’application du droit canadien, provincial ou étranger, de la tenue d’enquêtes liées à ce contrôle d’application ou de la collecte de renseignements en matière de sécurité en vue de ce contrôle d’application,
+(iii) qu’elle est demandée pour l’application du droit canadien ou provincial,
+(iv) qu’elle est demandée afin d’entrer en contact avec le plus proche parent d’un individu blessé, malade ou décédé, ou avec son représentant autorisé;
+c.2) elle est faite au titre de l’article 7 de la Loi sur le recyclage des produits de la criminalité et le financement des activités terroristes à l’institution gouvernementale mentionnée à cet article;
+d) elle est faite, à l’initiative de l’organisation, à une institution gouvernementale ou une subdivision d’une telle institution et l’organisation :
+(i) soit a des motifs raisonnables de croire que le renseignement est afférent à une contravention au droit fédéral, provincial ou étranger qui a été commise ou est en train ou sur le point de l’être,
+(ii) soit soupçonne que le renseignement est afférent à la sécurité nationale, à la défense du Canada ou à la conduite des affaires internationales;
+d.1) elle est faite à une autre organisation et est raisonnable en vue d’une enquête sur la violation d’un accord ou sur la contravention au droit fédéral ou provincial qui a été commise ou est en train ou sur le point de l’être, s’il est raisonnable de s’attendre à ce que la communication effectuée au su ou avec le consentement de l’intéressé compromettrait l’enquête;
+d.2) elle est faite à une autre organisation et est raisonnable en vue de la détection d’une fraude ou de sa suppression ou en vue de la prévention d’une fraude dont la commission est vraisemblable, s’il est raisonnable de s’attendre à ce que la communication effectuée au su ou avec le consentement de l’intéressé compromettrait la capacité de prévenir la fraude, de la détecter ou d’y mettre fin;
+d.21) elle est faite à une autre organisation au titre du paragraphe 11.01(1) de la Loi sur le recyclage des produits de la criminalité et le financement des activités terroristes;
+d.3) elle est faite, à l’initiative de l’organisation, à une institution gouvernementale ou à une subdivision d’une telle institution, au plus proche parent de l’intéressé ou à son représentant autorisé, si les conditions ci-après sont remplies :
+(i) l’organisation a des motifs raisonnables de croire que l’intéressé a été, est ou pourrait être victime d’exploitation financière,
+(ii) la communication est faite uniquement à des fins liées à la prévention de l’exploitation ou à une enquête y ayant trait,
+(iii) il est raisonnable de s’attendre à ce que la communication effectuée au su ou avec le consentement de l’intéressé compromettrait la capacité de prévenir l’exploitation ou d’enquêter sur celle-ci;
+d.4) elle est nécessaire aux fins d’identification de l’intéressé qui est blessé, malade ou décédé et est faite à une institution gouvernementale ou à une subdivision d’une telle institution, à un proche parent de l’intéressé ou à son représentant autorisé et, si l’intéressé est vivant, l’organisation en informe celui-ci par écrit et sans délai;
+e) elle est faite à toute personne qui a besoin du renseignement en raison d’une situation d’urgence mettant en danger la vie, la santé ou la sécurité de toute personne et, dans le cas où la personne visée par le renseignement est vivante, l’organisation en informe par écrit et sans délai cette dernière;
+e.1) il s’agit d’un renseignement contenu dans la déclaration d’un témoin et dont la communication est nécessaire en vue de l’évaluation d’une réclamation d’assurance, de son traitement ou de son règlement;
+e.2) il s’agit d’un renseignement produit par l’intéressé dans le cadre de son emploi, de son entreprise, ou de sa profession, et dont la communication est compatible avec les fins auxquelles il a été produit;
+f) la communication est faite à des fins statistiques ou à des fins d’étude ou de recherche érudites, ces fins ne peuvent être réalisées sans que le renseignement soit communiqué, le consentement est pratiquement impossible à obtenir et l’organisation informe le commissaire de la communication avant de la faire;
+g) elle est faite à une institution dont les attributions comprennent la conservation de documents ayant une importance historique ou archivistique, en vue d’une telle conservation;
+h) elle est faite cent ans ou plus après la constitution du document contenant le renseignement ou, en cas de décès de l’intéressé, vingt ans ou plus après le décès, dans la limite de cent ans;
+h.1) il s’agit d’un renseignement réglementaire auquel le public a accès;
+h.2) [Abrogé, 2015, ch. 32, art. 6]
+i) la communication est exigée par la loi.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>10.1.b</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Organizations must maintain and keep a record of every breach of security safeguards involving personal information under the organization's control for 24 months. The organization must provide the Privacy Commissioner with access to the record upon request.</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Les organisations doivent tenir un registre de toutes les atteintes aux mesures de sécurité impliquant des renseignements personnels sous leur contrôle pendant 24 mois. L'organisation doit donner au Commissaire accès à ce registre sur demande.</t>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Report to Commissioner</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Déclaration au commissaire</t>
         </is>
       </c>
     </row>
@@ -2439,52 +2392,53 @@
           <t>x</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>3</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10.1.c</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>The notification to affected individuals must be given as soon as feasible and contain sufficient information to allow the individual to understand the significance of the breach and to take steps, if any are possible, to reduce the risk of harm or to mitigate harm.</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>La notification aux personnes concernées doit être donnée dès que possible et contenir suffisamment d'informations pour permettre à la personne de comprendre l'importance de l'atteinte et de prendre des mesures, si possible, pour réduire le risque de préjudice ou atténuer ce dernier.</t>
+          <t>10.1-1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>An organization shall report to the Commissioner any breach of security safeguards involving personal information under its control if it is reasonable in the circumstances to believe that the breach creates a real risk of significant harm to an individual.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>L’organisation déclare au commissaire toute atteinte aux mesures de sécurité qui a trait à des renseignements personnels dont elle a la gestion, s’il est raisonnable de croire, dans les circonstances, que l’atteinte présente un risque réel de préjudice grave à l’endroit d’un individu.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="n">
-        <v>2</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>s. 7(3)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Disclosure Without Knowledge or Consent</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Limited circumstances in which personal information may be disclosed without the knowledge or consent of the individual.</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Communication sans connaissance ni consentement</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>10.1-3</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Unless otherwise prohibited by law, an organization shall notify an individual of any breach of security safeguards involving the individual’s personal information under the organization’s control if it is reasonable in the circumstances to believe that the breach creates a real risk of significant harm to the individual.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>À moins qu’une règle de droit ne l’interdise, l’organisation est tenue d’aviser l’intéressé de toute atteinte aux mesures de sécurité qui a trait à des renseignements personnels le concernant et dont elle a la gestion, s’il est raisonnable de croire, dans les circonstances, que l’atteinte présente un risque réel de préjudice grave à son endroit.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2492,24 +2446,176 @@
           <t>x</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>3</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>7(3).a</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Organizations may disclose personal information without knowledge or consent only in the specific circumstances listed in s. 7(3) of PIPEDA, including where required by law, for law enforcement purposes, to a lawyer representing the organization, or in an emergency that threatens life, health, or safety.</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Les organisations ne peuvent communiquer des renseignements personnels sans connaissance ni consentement que dans les cas spécifiques énoncés au par. 7(3) de la LPRPDE, notamment lorsque la loi l'exige, à des fins d'application de la loi, à l'avocat de l'organisation ou dans une situation d'urgence menaçant la vie, la santé ou la sécurité.</t>
+          <t>10.1-4</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>The notification shall contain sufficient information to allow the individual to understand the significance to them of the breach and to take steps, if any are possible, to reduce the risk of harm that could result from it or to mitigate that harm. It shall also contain any other prescribed information.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>L’avis contient suffisamment d’information pour permettre à l’intéressé de comprendre l’importance, pour lui, de l’atteinte et de prendre, si cela est possible, des mesures pour réduire le risque de préjudice qui pourrait en résulter ou pour atténuer un tel préjudice. Il contient aussi tout autre renseignement réglementaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10.1-6</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>The notification shall be given as soon as feasible after the organization determines that the breach has occurred.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>L’avis est donné le plus tôt possible après que l’organisation a conclu qu’il y a eu atteinte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Notification to organizations</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Avis à une organisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>10.2-1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>An organization that notifies an individual of a breach of security safeguards under subsection 10.1(3) shall notify any other organization, a government institution or a part of a government institution of the breach if the notifying organization believes that the other organization or the government institution or part concerned may be able to reduce the risk of harm that could result from it or mitigate that harm, or if any of the prescribed conditions are satisfied.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>L’organisation qui, en application du paragraphe 10.1(3), avise un individu d’une atteinte aux mesures de sécurité est tenue d’en aviser toute autre organisation, ou toute institution gouvernementale ou subdivision d’une telle institution, si elle croit que l’autre organisation, l’institution ou la subdivision peut être en mesure de réduire le risque de préjudice pouvant résulter de l’atteinte ou d’atténuer ce préjudice, ou s’il est satisfait à des conditions précisées par règlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Records</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Registre</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10.3-1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>An organization shall, in accordance with any prescribed requirements, keep and maintain a record of every breach of security safeguards involving personal information under its control.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>L’organisation tient et conserve, conformément aux règlements, un registre de toutes les atteintes aux mesures de sécurité qui ont trait à des renseignements personnels dont elle a la gestion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>10.3-2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>An organization shall, on request, provide the Commissioner with access to, or a copy of, a record.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sur demande du commissaire, l’organisation lui donne accès à son registre ou lui en remet copie.</t>
         </is>
       </c>
     </row>
